--- a/Models/Яйца/results/Яйца - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/Яйца/results/Яйца - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4692.09</v>
+        <v>2767.42</v>
       </c>
       <c r="C2" t="n">
-        <v>4184.81</v>
+        <v>2527.79</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1595.96</v>
+        <v>2416.51</v>
       </c>
       <c r="C3" t="n">
-        <v>1475.19</v>
+        <v>2292.86</v>
       </c>
       <c r="D3" t="n">
-        <v>7.95</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7727.78</v>
+        <v>6669.5</v>
       </c>
       <c r="C4" t="n">
-        <v>7394.82</v>
+        <v>6234.8</v>
       </c>
       <c r="D4" t="n">
-        <v>16.39</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2045.62</v>
+        <v>3201.92</v>
       </c>
       <c r="C5" t="n">
-        <v>2028.18</v>
+        <v>3188.79</v>
       </c>
       <c r="D5" t="n">
-        <v>82.17</v>
+        <v>80.04000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1141.05</v>
+        <v>536.02</v>
       </c>
       <c r="C6" t="n">
-        <v>1121.65</v>
+        <v>493.53</v>
       </c>
       <c r="D6" t="n">
-        <v>20.98</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="C7" t="n">
-        <v>6.19</v>
+        <v>5.66</v>
       </c>
       <c r="D7" t="n">
         <v>38.15</v>
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C8" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D8" t="n">
-        <v>75.83</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>909.73</v>
+        <v>1942.62</v>
       </c>
       <c r="C9" t="n">
-        <v>779.78</v>
+        <v>1798.74</v>
       </c>
       <c r="D9" t="n">
-        <v>5.36</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1475.1</v>
+        <v>1535.33</v>
       </c>
       <c r="C10" t="n">
-        <v>1396.37</v>
+        <v>1487.32</v>
       </c>
       <c r="D10" t="n">
-        <v>13.42</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1170.88</v>
+        <v>953.55</v>
       </c>
       <c r="C11" t="n">
-        <v>1032.42</v>
+        <v>838.84</v>
       </c>
       <c r="D11" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5089.6</v>
+        <v>4675.23</v>
       </c>
       <c r="C12" t="n">
-        <v>4935.93</v>
+        <v>4455.4</v>
       </c>
       <c r="D12" t="n">
-        <v>9.550000000000001</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6125.48</v>
+        <v>7387.24</v>
       </c>
       <c r="C13" t="n">
-        <v>5540.4</v>
+        <v>6544.02</v>
       </c>
       <c r="D13" t="n">
-        <v>16.75</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48.88</v>
+        <v>68.62</v>
       </c>
       <c r="C14" t="n">
-        <v>40.88</v>
+        <v>64.98</v>
       </c>
       <c r="D14" t="n">
-        <v>5.42</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.06</v>
+        <v>23.04</v>
       </c>
       <c r="C15" t="n">
-        <v>30.82</v>
+        <v>21.91</v>
       </c>
       <c r="D15" t="n">
-        <v>48.11</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2206.86</v>
+        <v>1098.24</v>
       </c>
       <c r="C16" t="n">
-        <v>2052.08</v>
+        <v>905.41</v>
       </c>
       <c r="D16" t="n">
-        <v>40.08</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4565.28</v>
+        <v>6163.21</v>
       </c>
       <c r="C17" t="n">
-        <v>3831.05</v>
+        <v>5290.43</v>
       </c>
       <c r="D17" t="n">
-        <v>13.71</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>635.0700000000001</v>
+        <v>960.78</v>
       </c>
       <c r="C18" t="n">
-        <v>540.0700000000001</v>
+        <v>878.03</v>
       </c>
       <c r="D18" t="n">
-        <v>46.92</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1104.83</v>
+        <v>1052.1</v>
       </c>
       <c r="C19" t="n">
-        <v>1035.94</v>
+        <v>955.97</v>
       </c>
       <c r="D19" t="n">
-        <v>6.29</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9656.99</v>
+        <v>8210.059999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>8515</v>
+        <v>7626.58</v>
       </c>
       <c r="D20" t="n">
-        <v>16.81</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2120.32</v>
+        <v>2211.14</v>
       </c>
       <c r="C21" t="n">
-        <v>1844.26</v>
+        <v>2134.12</v>
       </c>
       <c r="D21" t="n">
-        <v>9.27</v>
+        <v>10.14</v>
       </c>
     </row>
   </sheetData>
